--- a/study_case_model/bigger_network/scenario_variables/price_scenarios152.xlsx
+++ b/study_case_model/bigger_network/scenario_variables/price_scenarios152.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.416702360045</v>
+        <v>33.49592438445312</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.68180530718405</v>
+        <v>27.41472613226755</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.8552953801677</v>
+        <v>30.16765584372075</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.37056492355233</v>
+        <v>20.38192599373627</v>
       </c>
     </row>
     <row r="6">
@@ -519,15 +519,15 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.11872554310184</v>
+        <v>32.75876722855079</v>
       </c>
     </row>
     <row r="7">
@@ -539,11 +539,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.59474244477648</v>
+        <v>27.17082064563153</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.56928322813532</v>
+        <v>30.06345979949946</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.96212221277759</v>
+        <v>20.6595946665824</v>
       </c>
     </row>
     <row r="10">
@@ -583,15 +583,15 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.29149387066097</v>
+        <v>27.51551466689234</v>
       </c>
     </row>
     <row r="11">
@@ -599,15 +599,15 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.10493825262535</v>
+        <v>27.81145630025179</v>
       </c>
     </row>
     <row r="12">
@@ -619,11 +619,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27.12445164247194</v>
+        <v>26.63305390153197</v>
       </c>
     </row>
     <row r="13">
@@ -635,11 +635,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33.12476542513664</v>
+        <v>27.35945856730343</v>
       </c>
     </row>
     <row r="14">
@@ -647,15 +647,15 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.65285208666192</v>
+        <v>27.23566935342995</v>
       </c>
     </row>
     <row r="15">
@@ -663,15 +663,15 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.50596245049548</v>
+        <v>28.48375237616769</v>
       </c>
     </row>
     <row r="16">
@@ -679,15 +679,15 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.44524709129028</v>
+        <v>26.82071890962033</v>
       </c>
     </row>
     <row r="17">
@@ -699,11 +699,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.62469473362441</v>
+        <v>27.72100042623412</v>
       </c>
     </row>
     <row r="18">
@@ -711,15 +711,15 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33.16248136481905</v>
+        <v>27.02939264639835</v>
       </c>
     </row>
     <row r="19">
@@ -727,15 +727,15 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.24281772469002</v>
+        <v>27.09920350422753</v>
       </c>
     </row>
     <row r="20">
@@ -743,7 +743,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.92388282936668</v>
+        <v>28.28827949082092</v>
       </c>
     </row>
     <row r="21">
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.01949906210304</v>
+        <v>33.54799890995861</v>
       </c>
     </row>
     <row r="22">
@@ -775,7 +775,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.55156312230822</v>
+        <v>27.12753377726773</v>
       </c>
     </row>
     <row r="23">
@@ -791,7 +791,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.02446302032637</v>
+        <v>27.13278934287936</v>
       </c>
     </row>
     <row r="24">
@@ -807,15 +807,15 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.50485816430386</v>
+        <v>27.882950343186</v>
       </c>
     </row>
     <row r="25">
@@ -823,15 +823,15 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.42249081379442</v>
+        <v>32.82645860739984</v>
       </c>
     </row>
     <row r="26">
@@ -839,15 +839,15 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.06651176873098</v>
+        <v>29.19617249828903</v>
       </c>
     </row>
     <row r="27">
@@ -855,15 +855,15 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25.66880612220536</v>
+        <v>25.37799032970912</v>
       </c>
     </row>
     <row r="28">
@@ -871,15 +871,15 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>28.60970031210099</v>
+        <v>32.44425475306169</v>
       </c>
     </row>
     <row r="29">
@@ -887,15 +887,15 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>22.44560835660898</v>
+        <v>21.45184720469373</v>
       </c>
     </row>
     <row r="30">
@@ -903,15 +903,15 @@
         <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26.03931382476844</v>
+        <v>29.06559094412541</v>
       </c>
     </row>
     <row r="31">
@@ -919,15 +919,15 @@
         <v>3</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.23573116645012</v>
+        <v>24.87688167365211</v>
       </c>
     </row>
     <row r="32">
@@ -935,15 +935,15 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.07314384442957</v>
+        <v>32.58497134145912</v>
       </c>
     </row>
     <row r="33">
@@ -951,15 +951,15 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28.5815362448472</v>
+        <v>21.56536888754603</v>
       </c>
     </row>
     <row r="34">
@@ -967,15 +967,15 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>28.08520949642142</v>
+        <v>29.59509787426753</v>
       </c>
     </row>
     <row r="35">
@@ -983,15 +983,15 @@
         <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.94588944009113</v>
+        <v>22.86517068481368</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +999,15 @@
         <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20.07017554808181</v>
+        <v>25.33390358904544</v>
       </c>
     </row>
     <row r="37">
@@ -1015,15 +1015,15 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>30.98529814591621</v>
+        <v>26.98776369999537</v>
       </c>
     </row>
     <row r="38">
@@ -1031,15 +1031,15 @@
         <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.74053616513872</v>
+        <v>29.63147532324746</v>
       </c>
     </row>
     <row r="39">
@@ -1047,15 +1047,15 @@
         <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27.76717057398501</v>
+        <v>22.44560835660898</v>
       </c>
     </row>
     <row r="40">
@@ -1063,7 +1063,7 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28.94254623475594</v>
+        <v>26.03931382476844</v>
       </c>
     </row>
     <row r="41">
@@ -1079,7 +1079,7 @@
         <v>3</v>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1087,167 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.3376175598914</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>3</v>
-      </c>
-      <c r="B42" t="n">
-        <v>9</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ZEEBRUGGE</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>26.93857774432804</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>3</v>
-      </c>
-      <c r="B43" t="n">
-        <v>9</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>EMDEN</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>26.96893856639961</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>3</v>
-      </c>
-      <c r="B44" t="n">
-        <v>9</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>30.74258700110065</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>3</v>
-      </c>
-      <c r="B45" t="n">
-        <v>9</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>30.92917850353494</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>3</v>
-      </c>
-      <c r="B46" t="n">
-        <v>9</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>19.04915606862044</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>3</v>
-      </c>
-      <c r="B47" t="n">
-        <v>10</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ZEEBRUGGE</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>26.51858404071708</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" t="n">
-        <v>10</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>EMDEN</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>26.78930579343714</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>3</v>
-      </c>
-      <c r="B49" t="n">
-        <v>10</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>31.04076479487714</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" t="n">
-        <v>10</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>31.03244161801488</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>3</v>
-      </c>
-      <c r="B51" t="n">
-        <v>10</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>19.0792806143146</v>
+        <v>26.23573116645012</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/bigger_network/scenario_variables/price_scenarios152.xlsx
+++ b/study_case_model/bigger_network/scenario_variables/price_scenarios152.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33.49592438445312</v>
+        <v>29.416702360045</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.41472613226755</v>
+        <v>24.68180530718405</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.16765584372075</v>
+        <v>28.8552953801677</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.38192599373627</v>
+        <v>28.37056492355233</v>
       </c>
     </row>
     <row r="6">
@@ -519,15 +519,15 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.75876722855079</v>
+        <v>25.11872554310184</v>
       </c>
     </row>
     <row r="7">
@@ -539,11 +539,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.17082064563153</v>
+        <v>29.59474244477648</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.06345979949946</v>
+        <v>24.56928322813532</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.6595946665824</v>
+        <v>28.96212221277759</v>
       </c>
     </row>
     <row r="10">
@@ -583,15 +583,15 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.51551466689234</v>
+        <v>28.29149387066097</v>
       </c>
     </row>
     <row r="11">
@@ -599,15 +599,15 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.81145630025179</v>
+        <v>25.10493825262535</v>
       </c>
     </row>
     <row r="12">
@@ -619,11 +619,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26.63305390153197</v>
+        <v>27.12445164247194</v>
       </c>
     </row>
     <row r="13">
@@ -635,11 +635,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.35945856730343</v>
+        <v>33.12476542513664</v>
       </c>
     </row>
     <row r="14">
@@ -647,15 +647,15 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.23566935342995</v>
+        <v>27.65285208666192</v>
       </c>
     </row>
     <row r="15">
@@ -663,15 +663,15 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.48375237616769</v>
+        <v>26.50596245049548</v>
       </c>
     </row>
     <row r="16">
@@ -679,15 +679,15 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.82071890962033</v>
+        <v>29.44524709129028</v>
       </c>
     </row>
     <row r="17">
@@ -699,11 +699,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.72100042623412</v>
+        <v>27.62469473362441</v>
       </c>
     </row>
     <row r="18">
@@ -711,15 +711,15 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.02939264639835</v>
+        <v>33.16248136481905</v>
       </c>
     </row>
     <row r="19">
@@ -727,15 +727,15 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27.09920350422753</v>
+        <v>28.24281772469002</v>
       </c>
     </row>
     <row r="20">
@@ -743,7 +743,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.28827949082092</v>
+        <v>26.92388282936668</v>
       </c>
     </row>
     <row r="21">
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33.54799890995861</v>
+        <v>29.01949906210304</v>
       </c>
     </row>
     <row r="22">
@@ -775,7 +775,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.12753377726773</v>
+        <v>25.55156312230822</v>
       </c>
     </row>
     <row r="23">
@@ -791,7 +791,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.13278934287936</v>
+        <v>29.02446302032637</v>
       </c>
     </row>
     <row r="24">
@@ -807,15 +807,15 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.882950343186</v>
+        <v>22.50485816430386</v>
       </c>
     </row>
     <row r="25">
@@ -823,15 +823,15 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.82645860739984</v>
+        <v>26.42249081379442</v>
       </c>
     </row>
     <row r="26">
@@ -839,15 +839,15 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.19617249828903</v>
+        <v>26.06651176873098</v>
       </c>
     </row>
     <row r="27">
@@ -855,15 +855,15 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25.37799032970912</v>
+        <v>25.66880612220536</v>
       </c>
     </row>
     <row r="28">
@@ -871,15 +871,15 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32.44425475306169</v>
+        <v>28.60970031210099</v>
       </c>
     </row>
     <row r="29">
@@ -887,15 +887,15 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21.45184720469373</v>
+        <v>22.44560835660898</v>
       </c>
     </row>
     <row r="30">
@@ -903,15 +903,15 @@
         <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.06559094412541</v>
+        <v>26.03931382476844</v>
       </c>
     </row>
     <row r="31">
@@ -919,15 +919,15 @@
         <v>3</v>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.87688167365211</v>
+        <v>26.23573116645012</v>
       </c>
     </row>
     <row r="32">
@@ -935,15 +935,15 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>32.58497134145912</v>
+        <v>31.07314384442957</v>
       </c>
     </row>
     <row r="33">
@@ -951,15 +951,15 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21.56536888754603</v>
+        <v>28.5815362448472</v>
       </c>
     </row>
     <row r="34">
@@ -967,15 +967,15 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.59509787426753</v>
+        <v>28.08520949642142</v>
       </c>
     </row>
     <row r="35">
@@ -983,15 +983,15 @@
         <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>22.86517068481368</v>
+        <v>28.94588944009113</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +999,15 @@
         <v>3</v>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>25.33390358904544</v>
+        <v>20.07017554808181</v>
       </c>
     </row>
     <row r="37">
@@ -1015,15 +1015,15 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26.98776369999537</v>
+        <v>30.98529814591621</v>
       </c>
     </row>
     <row r="38">
@@ -1031,15 +1031,15 @@
         <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>29.63147532324746</v>
+        <v>28.74053616513872</v>
       </c>
     </row>
     <row r="39">
@@ -1047,15 +1047,15 @@
         <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>22.44560835660898</v>
+        <v>27.76717057398501</v>
       </c>
     </row>
     <row r="40">
@@ -1063,7 +1063,7 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>26.03931382476844</v>
+        <v>28.94254623475594</v>
       </c>
     </row>
     <row r="41">
@@ -1079,15 +1079,175 @@
         <v>3</v>
       </c>
       <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20.3376175598914</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>26.93857774432804</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>26.96893856639961</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>30.74258700110065</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>30.92917850353494</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EASINGTON</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>19.04915606862044</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="n">
         <v>10</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>26.51858404071708</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EMDEN</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>26.78930579343714</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>31.04076479487714</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DUNKERQUE</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>31.03244161801488</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>EASINGTON</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>26.23573116645012</v>
+      <c r="D51" t="n">
+        <v>19.0792806143146</v>
       </c>
     </row>
   </sheetData>
